--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-12T11:56:44+00:00</t>
+    <t>2025-02-18T15:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:23:31+00:00</t>
+    <t>2025-02-20T16:18:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:18:31+00:00</t>
+    <t>2025-02-20T16:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T16:32:32+00:00</t>
+    <t>2025-02-20T17:12:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T17:12:55+00:00</t>
+    <t>2025-02-24T09:51:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T09:51:08+00:00</t>
+    <t>2025-02-25T09:09:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T09:09:15+00:00</t>
+    <t>2025-03-05T10:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>name</t>
+    <t>CDA - name</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T10:03:58+00:00</t>
+    <t>2025-04-22T14:43:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -685,42 +685,42 @@
   <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="26.4921875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="26.4921875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="23.4765625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="22.7109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="22.7109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="20.125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="61.3203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="52.5703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="53.62890625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.0859375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="45.9765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="14.6484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-22T14:43:59+00:00</t>
+    <t>2025-04-23T09:14:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:14:13+00:00</t>
+    <t>2025-05-19T09:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-19T09:31:54+00:00</t>
+    <t>2025-05-20T13:20:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:20:55+00:00</t>
+    <t>2025-05-23T08:30:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T08:30:51+00:00</t>
+    <t>2025-05-23T15:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T15:44:19+00:00</t>
+    <t>2025-08-01T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-01T08:11:50+00:00</t>
+    <t>2025-08-22T10:16:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>CDA - name</t>
+    <t xml:space="preserve">CDA - </t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-22T10:16:53+00:00</t>
+    <t>2025-08-25T15:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'élément de l'en-tête du CDA name correspond au nom d'une personne physique.</t>
+    <t>L'élément de l'en-tête du CDA  correspond au nom d'une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -105,12 +105,12 @@
     <t>Type</t>
   </si>
   <si>
+    <t>http://hl7.org/cda/stds/core/StructureDefinition/PN</t>
+  </si>
+  <si>
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/cda/stds/core/StructureDefinition/PN</t>
-  </si>
-  <si>
     <t>Abstract</t>
   </si>
   <si>
@@ -120,7 +120,7 @@
     <t>Derivation</t>
   </si>
   <si>
-    <t>specialization</t>
+    <t>constraint</t>
   </si>
   <si>
     <t>ID</t>
@@ -234,7 +234,7 @@
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
-    <t>fr-core-name</t>
+    <t>PN</t>
   </si>
   <si>
     <t/>
@@ -250,6 +250,12 @@
 </t>
   </si>
   <si>
+    <t>Base for all types and resources</t>
+  </si>
+  <si>
+    <t>A name for a person. A sequence of name parts, such as given name or family name, prefix, suffix, etc. Examples for person name values are "Jim Bob Walton, Jr.", "Adam Everyman", etc. A person name may be as simple as a character string or may consist of several person name parts, such as, "Jim", "Bob", "Walton", and "Jr.". PN differs from EN because the qualifier type cannot include LS (Legal Status).</t>
+  </si>
+  <si>
     <t>Base</t>
   </si>
   <si>
@@ -263,7 +269,7 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>fr-core-name.nullFlavor</t>
+    <t>PN.nullFlavor</t>
   </si>
   <si>
     <t>Exceptional Value Detail</t>
@@ -285,7 +291,7 @@
     <t>ANY.nullFlavor</t>
   </si>
   <si>
-    <t>fr-core-name.use</t>
+    <t>PN.use</t>
   </si>
   <si>
     <t>Use Code</t>
@@ -300,7 +306,7 @@
     <t>EN.use</t>
   </si>
   <si>
-    <t>fr-core-name.item</t>
+    <t>PN.item</t>
   </si>
   <si>
     <t xml:space="preserve">Base
@@ -317,7 +323,7 @@
 </t>
   </si>
   <si>
-    <t>fr-core-name.item.delimiter</t>
+    <t>PN.item.delimiter</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
@@ -327,31 +333,49 @@
     <t>EN.item.delimiter</t>
   </si>
   <si>
-    <t>fr-core-name.item.family</t>
+    <t>PN.item.family</t>
+  </si>
+  <si>
+    <t>Nom de famille ou nom d’usage</t>
   </si>
   <si>
     <t>EN.item.family</t>
   </si>
   <si>
-    <t>fr-core-name.item.given</t>
+    <t>PN.item.given</t>
+  </si>
+  <si>
+    <t>Prénom</t>
   </si>
   <si>
     <t>EN.item.given</t>
   </si>
   <si>
-    <t>fr-core-name.item.prefix</t>
+    <t>PN.item.prefix</t>
+  </si>
+  <si>
+    <t>Civilité</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS</t>
   </si>
   <si>
     <t>EN.item.prefix</t>
   </si>
   <si>
-    <t>fr-core-name.item.suffix</t>
+    <t>PN.item.suffix</t>
+  </si>
+  <si>
+    <t>Titre</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J246-Titre-CISIS/FHIR/JDV-J246-Titre-CISIS</t>
   </si>
   <si>
     <t>EN.item.suffix</t>
   </si>
   <si>
-    <t>fr-core-name.item.xmlText</t>
+    <t>PN.item.xmlText</t>
   </si>
   <si>
     <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/st-simple}
@@ -367,7 +391,7 @@
     <t>EN.item.xmlText</t>
   </si>
   <si>
-    <t>fr-core-name.validTime</t>
+    <t>PN.validTime</t>
   </si>
   <si>
     <t>Valid Time</t>
@@ -648,15 +672,15 @@
         <v>29</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -685,8 +709,8 @@
   <dimension ref="A1:AK12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="22.7109375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="14.60546875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="14.60546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="20.125" customWidth="true" bestFit="true"/>
@@ -710,7 +734,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="45.9765625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.7265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -867,10 +891,10 @@
         <v>77</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -921,10 +945,10 @@
         <v>74</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>76</v>
@@ -933,31 +957,31 @@
         <v>74</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -969,11 +993,11 @@
         <v>74</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1000,11 +1024,11 @@
         <v>74</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>74</v>
@@ -1022,10 +1046,10 @@
         <v>74</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH3" t="s" s="2">
         <v>75</v>
@@ -1042,23 +1066,23 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>74</v>
@@ -1070,11 +1094,11 @@
         <v>74</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1101,11 +1125,11 @@
         <v>74</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="Y4" s="2"/>
       <c r="Z4" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AA4" t="s" s="2">
         <v>74</v>
@@ -1123,10 +1147,10 @@
         <v>74</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>76</v>
@@ -1143,10 +1167,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1169,11 +1193,11 @@
         <v>74</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1224,10 +1248,10 @@
         <v>74</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH5" t="s" s="2">
         <v>76</v>
@@ -1236,7 +1260,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1244,10 +1268,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1255,10 +1279,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1270,7 +1294,7 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1323,10 +1347,10 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH6" t="s" s="2">
         <v>76</v>
@@ -1343,10 +1367,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1354,7 +1378,7 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G7" t="s" s="2">
         <v>76</v>
@@ -1369,9 +1393,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L7" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1422,10 +1448,10 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH7" t="s" s="2">
         <v>76</v>
@@ -1442,10 +1468,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1453,10 +1479,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1468,9 +1494,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L8" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1521,10 +1549,10 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>76</v>
@@ -1541,10 +1569,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1552,10 +1580,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>74</v>
@@ -1567,9 +1595,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L9" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1596,13 +1626,11 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y9" s="2"/>
       <c r="Z9" t="s" s="2">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
@@ -1620,10 +1648,10 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>76</v>
@@ -1640,10 +1668,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1651,10 +1679,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
@@ -1666,9 +1694,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="L10" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1695,13 +1725,11 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y10" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y10" s="2"/>
       <c r="Z10" t="s" s="2">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -1719,10 +1747,10 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH10" t="s" s="2">
         <v>76</v>
@@ -1739,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1750,10 +1778,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -1765,14 +1793,14 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" t="s" s="2">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -1822,10 +1850,10 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH11" t="s" s="2">
         <v>75</v>
@@ -1842,23 +1870,23 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E12" t="s" s="2">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -1870,11 +1898,11 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="L12" s="2"/>
       <c r="M12" t="s" s="2">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1925,10 +1953,10 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AH12" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t xml:space="preserve">CDA - </t>
+    <t>CDA - Name</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:42:10+00:00</t>
+    <t>2025-10-02T14:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T14:05:03+00:00</t>
+    <t>2025-10-02T15:16:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-name.xlsx
+++ b/main/ig/StructureDefinition-fr-core-name.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-02T15:16:38+00:00</t>
+    <t>2025-10-13T15:21:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
